--- a/data/trans_dic/P1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,53</t>
+          <t>3,89; 7,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,26; 10,46</t>
+          <t>6,45; 10,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,83; 15,08</t>
+          <t>9,99; 15,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,78; 28,94</t>
+          <t>21,69; 28,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,42; 9,35</t>
+          <t>5,46; 9,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,99; 12,54</t>
+          <t>8,09; 12,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,74; 14,79</t>
+          <t>9,79; 14,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,82; 21,43</t>
+          <t>14,85; 21,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,2; 7,73</t>
+          <t>5,11; 7,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,82; 10,93</t>
+          <t>7,67; 10,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,61; 14,22</t>
+          <t>10,65; 14,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,8; 23,74</t>
+          <t>18,82; 23,97</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 7,61</t>
+          <t>4,28; 7,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 9,39</t>
+          <t>5,86; 9,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,67; 12,6</t>
+          <t>8,72; 12,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,37; 16,45</t>
+          <t>5,9; 16,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,37; 9,68</t>
+          <t>6,3; 9,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,92; 9,1</t>
+          <t>5,85; 9,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,96; 11,99</t>
+          <t>8,04; 12,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,29; 17,78</t>
+          <t>14,3; 17,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 8,14</t>
+          <t>5,65; 8,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,28; 8,57</t>
+          <t>6,2; 8,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,7; 11,66</t>
+          <t>8,79; 11,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,32; 16,36</t>
+          <t>8,89; 16,26</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,47; 9,94</t>
+          <t>5,57; 9,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,07; 10,54</t>
+          <t>6,35; 10,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,39; 15,64</t>
+          <t>10,79; 15,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,53; 18,92</t>
+          <t>13,33; 19,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,4; 13,02</t>
+          <t>8,04; 12,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,84; 11,24</t>
+          <t>6,71; 11,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,12; 15,21</t>
+          <t>9,93; 14,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,59; 14,34</t>
+          <t>5,18; 14,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,57; 10,85</t>
+          <t>7,42; 10,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,98; 10,09</t>
+          <t>6,94; 10,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,07; 14,5</t>
+          <t>10,93; 14,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,5; 15,29</t>
+          <t>8,69; 15,45</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,89; 11,86</t>
+          <t>8,11; 11,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 11,9</t>
+          <t>7,69; 11,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,41; 17,14</t>
+          <t>12,44; 17,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,68; 20,15</t>
+          <t>14,75; 19,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,9; 11,58</t>
+          <t>7,72; 11,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,04; 15,57</t>
+          <t>11,12; 15,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,48; 20,6</t>
+          <t>15,26; 20,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,71; 21,97</t>
+          <t>15,76; 22,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,47; 11,12</t>
+          <t>8,35; 11,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,02; 13,04</t>
+          <t>10,02; 12,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,79; 18,28</t>
+          <t>14,66; 18,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,16; 20,33</t>
+          <t>16,29; 20,37</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,4; 8,17</t>
+          <t>6,35; 8,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,36; 9,4</t>
+          <t>7,37; 9,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,55; 13,76</t>
+          <t>11,37; 13,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,92; 18,61</t>
+          <t>13,45; 18,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,8; 9,81</t>
+          <t>7,82; 9,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,9; 10,99</t>
+          <t>8,98; 11,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,92; 14,4</t>
+          <t>12,02; 14,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,16; 17,75</t>
+          <t>13,28; 17,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,35; 8,68</t>
+          <t>7,42; 8,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,47; 9,87</t>
+          <t>8,48; 9,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,02; 13,74</t>
+          <t>12,02; 13,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,29; 17,84</t>
+          <t>14,35; 17,84</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27955; 52232</t>
+          <t>26977; 52085</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44024; 73554</t>
+          <t>45384; 75703</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66332; 101775</t>
+          <t>67432; 103280</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>138404; 183900</t>
+          <t>137852; 181854</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>37339; 64391</t>
+          <t>37578; 63793</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55703; 87437</t>
+          <t>56386; 88760</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65510; 99530</t>
+          <t>65895; 98352</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>107488; 155432</t>
+          <t>107733; 155353</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>71822; 106864</t>
+          <t>70628; 108586</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>109584; 153042</t>
+          <t>107390; 150011</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>143025; 191580</t>
+          <t>143542; 193800</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>255797; 322985</t>
+          <t>256121; 326125</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42052; 73184</t>
+          <t>41154; 70217</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59686; 95569</t>
+          <t>59626; 95419</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88623; 128816</t>
+          <t>89150; 128606</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>75975; 196280</t>
+          <t>70427; 195819</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>61697; 93760</t>
+          <t>60996; 95183</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61090; 93976</t>
+          <t>60409; 94236</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83040; 125062</t>
+          <t>83870; 126589</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>137019; 170471</t>
+          <t>137081; 169779</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>110363; 157184</t>
+          <t>109059; 155084</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>128732; 175649</t>
+          <t>127066; 175689</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>179757; 240740</t>
+          <t>181576; 239747</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>200588; 352085</t>
+          <t>191279; 349874</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>37083; 67431</t>
+          <t>37817; 67647</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>46012; 79888</t>
+          <t>48121; 81028</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78899; 118811</t>
+          <t>81926; 121322</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95342; 133353</t>
+          <t>93941; 134278</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>57458; 89025</t>
+          <t>54964; 87910</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53149; 87330</t>
+          <t>52181; 85600</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79406; 119439</t>
+          <t>77937; 114944</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>52209; 133861</t>
+          <t>48355; 131433</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>103081; 147861</t>
+          <t>101101; 145894</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>107178; 154852</t>
+          <t>106476; 154280</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>170958; 224012</t>
+          <t>168881; 222981</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>139194; 250512</t>
+          <t>142303; 253091</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74297; 111748</t>
+          <t>76397; 112590</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74507; 112736</t>
+          <t>72868; 111691</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>116328; 160704</t>
+          <t>116629; 160940</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136013; 186765</t>
+          <t>136725; 184708</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>82020; 120244</t>
+          <t>80188; 119234</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>116149; 163779</t>
+          <t>116983; 162957</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>161589; 215009</t>
+          <t>159248; 213255</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>172059; 240521</t>
+          <t>172540; 243340</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>167774; 220284</t>
+          <t>165315; 220678</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>200265; 260802</t>
+          <t>200453; 257767</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>293032; 362230</t>
+          <t>290402; 359358</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>326724; 411097</t>
+          <t>329331; 411766</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>209536; 267820</t>
+          <t>208080; 268121</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>252379; 322286</t>
+          <t>252517; 323157</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>391908; 467061</t>
+          <t>385915; 462648</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>446849; 643924</t>
+          <t>465285; 645945</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>263461; 331569</t>
+          <t>264324; 329422</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>316856; 391205</t>
+          <t>319615; 393320</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>422524; 510518</t>
+          <t>426087; 512579</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>488579; 659073</t>
+          <t>493102; 660438</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>489298; 577801</t>
+          <t>494099; 579992</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>591395; 689537</t>
+          <t>592116; 694341</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>834114; 953145</t>
+          <t>834380; 950192</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1025000; 1279680</t>
+          <t>1029354; 1279637</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 7,5</t>
+          <t>4,01; 7,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,45; 10,76</t>
+          <t>6,28; 10,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,99; 15,31</t>
+          <t>10,1; 15,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,69; 28,62</t>
+          <t>21,3; 28,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,27</t>
+          <t>5,48; 9,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,09; 12,73</t>
+          <t>8,33; 12,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,79; 14,62</t>
+          <t>9,72; 14,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,85; 21,42</t>
+          <t>17,54; 22,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 7,86</t>
+          <t>5,14; 7,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,67; 10,71</t>
+          <t>7,78; 10,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,65; 14,38</t>
+          <t>10,62; 14,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,82; 23,97</t>
+          <t>20,22; 24,11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,3</t>
+          <t>4,44; 7,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 9,37</t>
+          <t>5,8; 9,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,72; 12,58</t>
+          <t>8,74; 12,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,9; 16,42</t>
+          <t>14,4; 19,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 9,83</t>
+          <t>6,2; 9,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 9,13</t>
+          <t>5,72; 9,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,04; 12,14</t>
+          <t>8,16; 12,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,3; 17,71</t>
+          <t>14,02; 17,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,65; 8,03</t>
+          <t>5,8; 8,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,2; 8,57</t>
+          <t>6,32; 8,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,79; 11,61</t>
+          <t>8,8; 11,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,89; 16,26</t>
+          <t>14,68; 17,7</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,57; 9,97</t>
+          <t>5,62; 10,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 10,69</t>
+          <t>6,12; 10,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,79; 15,97</t>
+          <t>10,63; 15,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,33; 19,06</t>
+          <t>14,15; 20,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,04; 12,86</t>
+          <t>8,21; 12,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,71; 11,01</t>
+          <t>6,8; 11,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,93; 14,64</t>
+          <t>10,23; 14,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 14,08</t>
+          <t>11,68; 15,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,42; 10,71</t>
+          <t>7,54; 10,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,94; 10,05</t>
+          <t>7,05; 10,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,93; 14,44</t>
+          <t>10,87; 14,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,69; 15,45</t>
+          <t>13,46; 17,22</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,11; 11,95</t>
+          <t>8,11; 11,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,69; 11,79</t>
+          <t>7,45; 11,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,44; 17,17</t>
+          <t>12,58; 17,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,75; 19,93</t>
+          <t>14,85; 19,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,72; 11,48</t>
+          <t>7,72; 11,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,12; 15,49</t>
+          <t>11,19; 15,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,26; 20,43</t>
+          <t>15,46; 20,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,76; 22,22</t>
+          <t>18,83; 22,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,35; 11,14</t>
+          <t>8,42; 11,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,02; 12,89</t>
+          <t>10,26; 13,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,66; 18,14</t>
+          <t>14,78; 18,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,29; 20,37</t>
+          <t>17,6; 20,69</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,35; 8,18</t>
+          <t>6,39; 8,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,43</t>
+          <t>7,45; 9,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,37; 13,63</t>
+          <t>11,37; 13,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,45; 18,67</t>
+          <t>17,04; 19,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,82; 9,75</t>
+          <t>7,74; 9,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,98; 11,05</t>
+          <t>8,95; 11,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,02; 14,46</t>
+          <t>12,04; 14,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,28; 17,79</t>
+          <t>16,56; 18,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,71</t>
+          <t>7,36; 8,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,48; 9,94</t>
+          <t>8,53; 9,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,02; 13,69</t>
+          <t>12,0; 13,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,35; 17,84</t>
+          <t>17,19; 18,85</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>158762</t>
+          <t>170635</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>136807</t>
+          <t>145812</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>295569</t>
+          <t>316446</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26977; 52085</t>
+          <t>27856; 50971</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>45384; 75703</t>
+          <t>44169; 73635</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67432; 103280</t>
+          <t>68128; 102229</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>137852; 181854</t>
+          <t>147097; 196937</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>37578; 63793</t>
+          <t>37756; 64686</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56386; 88760</t>
+          <t>58054; 89446</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65895; 98352</t>
+          <t>65374; 99959</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>107733; 155353</t>
+          <t>128806; 163705</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>70628; 108586</t>
+          <t>71007; 106000</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>107390; 150011</t>
+          <t>109007; 152552</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>143542; 193800</t>
+          <t>143155; 190326</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>256121; 326125</t>
+          <t>288175; 343515</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>148129</t>
+          <t>173990</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>152892</t>
+          <t>168262</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>301021</t>
+          <t>342252</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41154; 70217</t>
+          <t>42712; 70506</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59626; 95419</t>
+          <t>58992; 94636</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89150; 128606</t>
+          <t>89344; 128277</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>70427; 195819</t>
+          <t>150993; 201336</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60996; 95183</t>
+          <t>60051; 93962</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60409; 94236</t>
+          <t>59060; 95410</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83870; 126589</t>
+          <t>85117; 126294</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>137081; 169779</t>
+          <t>150246; 188223</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>109059; 155084</t>
+          <t>112014; 156470</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>127066; 175689</t>
+          <t>129632; 175910</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181576; 239747</t>
+          <t>181844; 241397</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>191279; 349874</t>
+          <t>311264; 375265</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>113387</t>
+          <t>136560</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>97784</t>
+          <t>111402</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>211172</t>
+          <t>247962</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>37817; 67647</t>
+          <t>38108; 69386</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48121; 81028</t>
+          <t>46340; 78833</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81926; 121322</t>
+          <t>80769; 117977</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93941; 134278</t>
+          <t>113614; 162108</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>54964; 87910</t>
+          <t>56116; 87285</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>52181; 85600</t>
+          <t>52820; 86054</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77937; 114944</t>
+          <t>80308; 117497</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>48355; 131433</t>
+          <t>94861; 128858</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>101101; 145894</t>
+          <t>102684; 147661</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>106476; 154280</t>
+          <t>108231; 154712</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>168881; 222981</t>
+          <t>167945; 224755</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>142303; 253091</t>
+          <t>217411; 278111</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159113</t>
+          <t>169792</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>215027</t>
+          <t>232058</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>374140</t>
+          <t>401850</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>76397; 112590</t>
+          <t>76398; 112138</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>72868; 111691</t>
+          <t>70604; 109046</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>116629; 160940</t>
+          <t>117959; 162033</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136725; 184708</t>
+          <t>147051; 194907</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>80188; 119234</t>
+          <t>80171; 120569</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>116983; 162957</t>
+          <t>117746; 161295</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>159248; 213255</t>
+          <t>161326; 214209</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>172540; 243340</t>
+          <t>210770; 256634</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>165315; 220678</t>
+          <t>166712; 222065</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>200453; 257767</t>
+          <t>205170; 262970</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>290402; 359358</t>
+          <t>292817; 358898</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>329331; 411766</t>
+          <t>371131; 436378</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>579391</t>
+          <t>650977</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>602510</t>
+          <t>657534</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1181902</t>
+          <t>1308510</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>208080; 268121</t>
+          <t>209412; 271884</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>252517; 323157</t>
+          <t>255201; 322954</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>385915; 462648</t>
+          <t>385870; 468053</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>465285; 645945</t>
+          <t>601919; 699677</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>264324; 329422</t>
+          <t>261588; 329584</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>319615; 393320</t>
+          <t>318571; 393250</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>426087; 512579</t>
+          <t>426715; 512088</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>493102; 660438</t>
+          <t>618777; 694281</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>494099; 579992</t>
+          <t>489979; 582606</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>592116; 694341</t>
+          <t>595702; 691765</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>834380; 950192</t>
+          <t>832352; 950207</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1029354; 1279637</t>
+          <t>1249391; 1369989</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
+          <t>Población que conforma un hogar unipersonal (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
+          <t>Población que conforma un hogar unipersonal (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
